--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/04-virtual-kitchen-duties-by-role.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/04-virtual-kitchen-duties-by-role.xlsx
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>Watch ticket times: target under 10 min prep</t>
+          <t>Watch ticket times: orders ready in 8-12 min</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -2098,9 +2098,9 @@
       <c r="A7" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="34" t="inlineStr">
-        <is>
-          <t>Turn on all brands in DoorDash, Uber Eats and Grubhub</t>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Check that menus are up to date</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>Check that menus are up to date</t>
+          <t>86 the dishes that are out of stock</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
@@ -2179,9 +2179,9 @@
       <c r="A10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>86 the dishes that are out of stock</t>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>Turn on all brands in DoorDash, Uber Eats and Grubhub</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
